--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260630.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260630.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>34,511</t>
+          <t>34,299</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.90%</t>
+          <t>11.39%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>83,418</t>
+          <t>82,908</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.76%</t>
+          <t>9.99%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>96,222</t>
+          <t>95,633</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.46%</t>
+          <t>9.05%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>37,876</t>
+          <t>37,644</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.75%</t>
+          <t>7.66%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>207,895</t>
+          <t>206,623</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.28%</t>
+          <t>5.13%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>52,193</t>
+          <t>51,874</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.44%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>110,567</t>
+          <t>109,890</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>119,914</t>
+          <t>119,180</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>20,644</t>
+          <t>20,518</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>62,808</t>
+          <t>62,423</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>124,726</t>
+          <t>123,963</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>57,767</t>
+          <t>57,413</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
@@ -875,56 +875,56 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>145,198</t>
+          <t>144,309</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>24,002</t>
+          <t>25,732</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>25,890</t>
+          <t>23,855</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>66,370</t>
+          <t>65,964</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>12,077</t>
+          <t>12,003</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>39,180</t>
+          <t>38,941</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>52,983</t>
+          <t>52,659</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>5,242</t>
+          <t>5,210</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>54,552</t>
+          <t>54,219</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>34,632</t>
+          <t>34,421</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>82,027</t>
+          <t>81,526</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>53,328</t>
+          <t>53,001</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>23,711</t>
+          <t>23,566</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1161,29 +1161,29 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>32,432</t>
+          <t>32,234</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>50,097</t>
+          <t>9,533</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,66 +1195,66 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>22,061</t>
+          <t>49,791</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>29,368</t>
+          <t>21,926</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>9,592</t>
+          <t>14,031</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1271,34 +1271,34 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,341</t>
+          <t>11,272</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>14,117</t>
+          <t>29,189</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>79,975</t>
+          <t>79,486</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>101,269</t>
+          <t>100,649</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>32,293</t>
+          <t>32,095</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>155,472</t>
+          <t>154,520</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>32,694</t>
+          <t>32,494</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>6,261</t>
+          <t>6,223</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1459,61 +1459,61 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>14,300</t>
+          <t>7,228</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>27,464</t>
+          <t>14,212</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>46,322</t>
+          <t>27,296</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,22 +1525,22 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>7,273</t>
+          <t>46,038</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>3,889</t>
+          <t>3,866</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>17,180</t>
+          <t>17,075</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>100,670</t>
+          <t>100,055</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>25,054</t>
+          <t>24,901</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>3,024</t>
+          <t>3,006</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>8,545</t>
+          <t>8,492</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>19,657</t>
+          <t>19,537</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>40,758</t>
+          <t>40,509</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>131,340,424</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
